--- a/SCRAPING/GAMBAR/wisataV2_updated_updated.xlsx
+++ b/SCRAPING/GAMBAR/wisataV2_updated_updated.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -646,9 +646,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/TRANS_Wisata_Belah_Duren</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -695,9 +699,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Candi_Bocok</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -744,9 +752,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Kasembon_Park</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -793,9 +805,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Fishing_Sultan_Class</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -842,9 +858,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Candi_Sapto</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -891,9 +911,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Wisata_Bukit_Gandrung,_Tanggulasi</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -940,9 +964,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Air_Terjun_Coban_Rondo_Pujon</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -989,9 +1017,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Taman_Wisata_Blendrang</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1038,9 +1070,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Taman_Wisata_Selorejo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1087,9 +1123,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Air_Terjun_Coban_Kethak</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1136,9 +1176,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Bukit_Nirwana</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1185,9 +1229,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Bukit_Teletubbies_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1234,9 +1282,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Brakseng</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1283,9 +1335,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Wisata_Rafting_Kali_Uceng_Desa_Kasembon</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1332,9 +1388,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Desa_Wisata_Pujonkidul</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1381,9 +1441,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Taman_Kemesraan</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1430,9 +1494,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pemandian_Sumber_Seger_Waras</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1479,9 +1547,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Jembatan_Gantung_Selorejo_Ngantang</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1528,9 +1600,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pasar_Wisata_Dewi_Sri</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1577,9 +1653,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Waduk_Selorejo</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1626,9 +1706,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Monumen_Palagan_Mendalan</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1667,9 +1751,13 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Watu_Gilang_(ꦮꦠꦸꦒꦶꦭꦁ)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1716,9 +1804,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Wisata_Desa_BONPI__de'_Asmorondono</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1765,9 +1857,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Bukit_Waung</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1814,9 +1910,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/TAMAN_WISATA_BEDENGAN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1863,9 +1963,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Pasir_Panjang_Ngeliyep</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1912,9 +2016,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Bukit_Nuri</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1961,9 +2069,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Teluk_BIDADARI_ꦠ꧀ꦭꦒꦮꦶꦢꦢꦫꦶ</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2010,9 +2122,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Ngliyep_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2059,9 +2175,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Wisata_Rowo_Klampok</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2108,9 +2228,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Goa_Pathuk_ilang_ꦥꦼꦱꦶꦱꦶꦂꦒꦸꦮꦥꦡꦸꦏ꧀ꦅꦭꦁ</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2149,9 +2273,13 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Nglurung_ꦥꦼꦱꦶꦱꦶꦂꦔ꧀ꦭꦸꦫꦸꦁ</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2198,9 +2326,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Wisata_Ngebrak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2247,9 +2379,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Ngledakan_Ciut_ꦥꦼꦱꦶꦱꦶꦂꦔ꧀ꦭꦼꦢꦏꦤ꧀ꦕꦶꦪꦸꦠ꧀</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2296,9 +2432,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Modangan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2345,9 +2485,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Pantai_Banyu_Anjlok</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2394,9 +2538,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>GAMBAR/wisata/Gunung_Geger</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
